--- a/data/trending_integrated_20261022_12.xlsx
+++ b/data/trending_integrated_20261022_12.xlsx
@@ -563,83 +563,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>빅텍</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>56000</v>
+        <v>3655</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+17.40%</t>
+          <t>'+18.28%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>275</v>
+        <v>228</v>
       </c>
       <c r="F2" t="n">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="G2" t="n">
-        <v>1132</v>
+        <v>457</v>
       </c>
       <c r="H2" t="n">
-        <v>37.72</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>47700</v>
+        <v>3090</v>
       </c>
       <c r="K2" t="n">
-        <v>51000</v>
+        <v>3190</v>
       </c>
       <c r="L2" t="n">
-        <v>56500</v>
+        <v>3870</v>
       </c>
       <c r="M2" t="n">
-        <v>50500</v>
+        <v>3155</v>
       </c>
       <c r="N2" t="n">
-        <v>37.7</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>489495545950</v>
+        <v>60289575693</v>
       </c>
       <c r="P2" t="n">
-        <v>67300</v>
+        <v>7050</v>
       </c>
       <c r="Q2" t="n">
-        <v>23150</v>
+        <v>2500</v>
       </c>
       <c r="R2" t="n">
-        <v>1412000</v>
+        <v>-28000</v>
       </c>
       <c r="S2" t="n">
-        <v>410000</v>
+        <v>150000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>삼성E&amp;A, 어닝 서프라이즈 및 주식 소각 결정, 전망 상향 공시. MSCI 편입 예상.</t>
+          <t>김정은 신변 이상설 제기 및 전쟁 가능성 부각. 관련주로 빅텍 주목, 단기 급등 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['어닝 서프라이즈', '주식 소각', '전망 상향']</t>
+          <t>['김정은', '신변이상설', '전쟁가능성']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,90 +648,90 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>065450</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>빅텍</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3625</v>
+        <v>55400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.31%</t>
+          <t>'+16.14%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>223</v>
+        <v>282</v>
       </c>
       <c r="F3" t="n">
-        <v>124</v>
+        <v>158</v>
       </c>
       <c r="G3" t="n">
-        <v>445</v>
+        <v>1181</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>37.72</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3090</v>
+        <v>47700</v>
       </c>
       <c r="K3" t="n">
-        <v>3190</v>
+        <v>51000</v>
       </c>
       <c r="L3" t="n">
-        <v>3870</v>
+        <v>56500</v>
       </c>
       <c r="M3" t="n">
-        <v>3155</v>
+        <v>50500</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>37.7</v>
       </c>
       <c r="O3" t="n">
-        <v>59622822991</v>
+        <v>496909122700</v>
       </c>
       <c r="P3" t="n">
-        <v>7050</v>
+        <v>67300</v>
       </c>
       <c r="Q3" t="n">
-        <v>2500</v>
+        <v>23150</v>
       </c>
       <c r="R3" t="n">
-        <v>-28000</v>
+        <v>1412000</v>
       </c>
       <c r="S3" t="n">
-        <v>150000</v>
+        <v>410000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>김정은 신변 이상설 및 전쟁 가능성 대두에 따른 급등. 단기적 테마주로서의 움직임.</t>
+          <t>호실적 발표, 주식 소각 결정, 전망 상향 등 긍정적 공시 잇따름. 외인 매수세 및 숏커버링 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['김정은 신변 이상설', '전쟁 가능성', '테마주']</t>
+          <t>['어닝서프라이즈', '주식소각', '실적전망']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>065450</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7400</v>
+        <v>7430</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+11.11%</t>
+          <t>'+11.56%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G4" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>8205879180</v>
+        <v>8277603860</v>
       </c>
       <c r="P4" t="n">
         <v>8430</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>로봇 관련 촉각 센서 기술 개발 및 현대차 파트너십을 기반으로 한 높은 기대감 표출. 미국 기업 루미아 인수 관련 구체적인 인수 의향서 및 본계약 언급.</t>
+          <t>루미아 인수 관련 로봇 기술 개발 기대감 고조. 현대차 파트너십 및 신규 기술 양산 가능성. 목표가 상향 제시.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['촉각 센서', '루미아 인수', '현대차']</t>
+          <t>['루미아인수', '로봇기술', '촉각센서']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1755</v>
+        <v>1700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.01%</t>
+          <t>'+5.59%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G5" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -886,7 +886,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>17430798923</v>
+        <v>18359958254</v>
       </c>
       <c r="P5" t="n">
         <v>3980</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18420</v>
+        <v>18200</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.79%</t>
+          <t>'+1.56%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.32</v>
       </c>
       <c r="E6" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F6" t="n">
         <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="H6" t="n">
         <v>3.29</v>
@@ -972,13 +972,13 @@
         <v>20150</v>
       </c>
       <c r="M6" t="n">
-        <v>18280</v>
+        <v>18100</v>
       </c>
       <c r="N6" t="n">
         <v>3.61</v>
       </c>
       <c r="O6" t="n">
-        <v>66256075060</v>
+        <v>67212052875</v>
       </c>
       <c r="P6" t="n">
         <v>22450</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14860</v>
+        <v>14820</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.61%</t>
+          <t>'+0.34%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.13</v>
       </c>
       <c r="E7" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="H7" t="n">
         <v>9.949999999999999</v>
@@ -1070,7 +1070,7 @@
         <v>9.82</v>
       </c>
       <c r="O7" t="n">
-        <v>31587662710</v>
+        <v>31959005585</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>건설주 전반의 상승 속에서 상대적 약세 언급. 정치 관련 언급 및 대차해지 요구.</t>
+          <t>건설주 전반의 상승 기대감 속에서 외국인 및 연기금 매수세 관찰. 삼성E&amp;A 대비 낮은 상승률 지적.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['건설주', '주가 부양', '대차해지']</t>
+          <t>['건설주', '외국인매수', '실적우량주']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14190</v>
+        <v>14070</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.84%</t>
+          <t>'-1.68%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>106</v>
       </c>
       <c r="F8" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G8" t="n">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="H8" t="n">
         <v>3.48</v>
@@ -1162,7 +1162,7 @@
         <v>3.15</v>
       </c>
       <c r="O8" t="n">
-        <v>84493073225</v>
+        <v>85787176605</v>
       </c>
       <c r="P8" t="n">
         <v>31500</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>AI 광통신 및 EUV용 유리기판 제조 기술 확보 관련 뉴스 언급. 기관 매집 시작 가능성 및 기술력에 대한 긍정적 평가.</t>
+          <t>AI 광통신 관련 기술 확보 소식 및 EUV용 유리기판 제조 기술 주목. 기관 매집 시작 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['AI 광통신', '유리기판', '기관 매집']</t>
+          <t>['AI광통신', '유리기판', '기관매집']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41800</v>
+        <v>41600</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.30%</t>
+          <t>'-1.77%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.14</v>
       </c>
       <c r="E9" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F9" t="n">
         <v>84</v>
       </c>
       <c r="G9" t="n">
-        <v>675</v>
+        <v>697</v>
       </c>
       <c r="H9" t="n">
         <v>13.09</v>
@@ -1254,7 +1254,7 @@
         <v>13.23</v>
       </c>
       <c r="O9" t="n">
-        <v>8925952900</v>
+        <v>9148827200</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7210</v>
+        <v>7200</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.90%</t>
+          <t>'-2.04%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.02</v>
       </c>
       <c r="E10" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F10" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="H10" t="n">
         <v>25.47</v>
@@ -1346,7 +1346,7 @@
         <v>25.45</v>
       </c>
       <c r="O10" t="n">
-        <v>8918538455</v>
+        <v>9084000655</v>
       </c>
       <c r="P10" t="n">
         <v>17950</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>지속된 적자와 낮은 주가에도 불구하고 과거 대규모 투자 언급. 신저가 수준의 낮은 PBR 기반 바닥론 제기.</t>
+          <t>연이은 적자 발표 및 주가 하락세 지속. 30년 최저가 수준 기록, PBR 0.57로 저평가 논란.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="G11" t="n">
-        <v>1306</v>
+        <v>1358</v>
       </c>
       <c r="H11" t="n">
         <v>46.14</v>
@@ -1438,7 +1438,7 @@
         <v>46.08</v>
       </c>
       <c r="O11" t="n">
-        <v>1185013021750</v>
+        <v>1212999818500</v>
       </c>
       <c r="P11" t="n">
         <v>374500</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 이슈와 특정 인물 관련 부정적 전망 및 증시 하락 예측.</t>
+          <t>정치적 이슈와 함께 개인 투자자 매도세 지속. 증시 하락 전망 및 불안감 고조.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['증시하락', '주가조작', '외국인매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14450</v>
+        <v>14410</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.54%</t>
+          <t>'-3.81%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>1.2</v>
       </c>
       <c r="E12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F12" t="n">
         <v>44</v>
       </c>
       <c r="G12" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H12" t="n">
         <v>1.2</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>71814893280</v>
+        <v>72085955400</v>
       </c>
       <c r="P12" t="n">
         <v>28800</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1248000</v>
+        <v>9750</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.55%</t>
+          <t>'-4.32%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.02</v>
+        <v>0.53</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>109</v>
       </c>
       <c r="F13" t="n">
-        <v>504</v>
+        <v>63</v>
       </c>
       <c r="G13" t="n">
-        <v>1687</v>
+        <v>305</v>
       </c>
       <c r="H13" t="n">
-        <v>48.79</v>
+        <v>5.87</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1294000</v>
+        <v>10190</v>
       </c>
       <c r="K13" t="n">
-        <v>1273000</v>
+        <v>10110</v>
       </c>
       <c r="L13" t="n">
-        <v>1297000</v>
+        <v>10180</v>
       </c>
       <c r="M13" t="n">
-        <v>1240000</v>
+        <v>9620</v>
       </c>
       <c r="N13" t="n">
-        <v>48.77</v>
+        <v>5.34</v>
       </c>
       <c r="O13" t="n">
-        <v>1396154889000</v>
+        <v>13533384050</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>14940</v>
       </c>
       <c r="Q13" t="n">
-        <v>468000</v>
+        <v>5390</v>
       </c>
       <c r="R13" t="n">
-        <v>-55000</v>
+        <v>-32000</v>
       </c>
       <c r="S13" t="n">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 이슈와 특정 인물에 대한 부정적 언급 및 반도체 산업 전반에 대한 비관론 제기.</t>
+          <t>테슬라 실적 발표 및 스페이스X 관련 뉴스에도 불구하고 주가 하락 및 공매도 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['테슬라', '스페이스X', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9790</v>
+        <v>1238000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.93%</t>
+          <t>'-4.33%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.53</v>
+        <v>0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>106</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>62</v>
+        <v>503</v>
       </c>
       <c r="G14" t="n">
-        <v>297</v>
+        <v>1687</v>
       </c>
       <c r="H14" t="n">
-        <v>5.87</v>
+        <v>48.79</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>10190</v>
+        <v>1294000</v>
       </c>
       <c r="K14" t="n">
-        <v>10110</v>
+        <v>1273000</v>
       </c>
       <c r="L14" t="n">
-        <v>10180</v>
+        <v>1297000</v>
       </c>
       <c r="M14" t="n">
-        <v>9620</v>
+        <v>1238000</v>
       </c>
       <c r="N14" t="n">
-        <v>5.34</v>
+        <v>48.77</v>
       </c>
       <c r="O14" t="n">
-        <v>13433706095</v>
+        <v>1452608194000</v>
       </c>
       <c r="P14" t="n">
-        <v>14940</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>5390</v>
+        <v>468000</v>
       </c>
       <c r="R14" t="n">
-        <v>-32000</v>
+        <v>-55000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-6000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>테슬라 실적 발표 및 스페이스X 관련 뉴스에도 불구하고 주가 하락 및 공매도 우려.</t>
+          <t>정치적 이슈와 맞물려 반도체 산업 하락 및 주가 하락세 지속. 외국인 매도세 관찰.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['테슬라', '스페이스X', '공매도']</t>
+          <t>['반도체산업', '주가하락', '외국인매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10080</v>
+        <v>10070</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-9.52%</t>
+          <t>'-9.61%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>2.41</v>
       </c>
       <c r="E15" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G15" t="n">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="H15" t="n">
         <v>3.69</v>
@@ -1806,7 +1806,7 @@
         <v>1.28</v>
       </c>
       <c r="O15" t="n">
-        <v>52019166015</v>
+        <v>52916716375</v>
       </c>
       <c r="P15" t="n">
         <v>11690</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>로봇주 전반의 급등 후 조정 및 투기적 거래 경고. ESS 마진율 불확실성 및 하락 파동 복구 어려움 언급.</t>
+          <t>로봇주 급등 후 조정 구간 진입, 투기적 매매 경계. ESS 마진율 불확실성 및 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['로봇주', '투기', 'ESS']</t>
+          <t>['로봇주', '투기', 'ESS마진율']</t>
         </is>
       </c>
       <c r="X15" t="n">

--- a/data/trending_integrated_20261022_12.xlsx
+++ b/data/trending_integrated_20261022_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3655</v>
+        <v>3695</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+18.28%</t>
+          <t>'+19.58%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="F2" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="G2" t="n">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>60289575693</v>
+        <v>62167598262</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -626,12 +626,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>김정은 신변 이상설 제기 및 전쟁 가능성 부각. 관련주로 빅텍 주목, 단기 급등 기대.</t>
+          <t>빅텍, 김정은 신변 이상설 및 사망설로 인한 급등. 전쟁 가능성 대두 및 단기 차익 실현 움직임.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55400</v>
+        <v>55300</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.14%</t>
+          <t>'+15.93%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="F3" t="n">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="G3" t="n">
-        <v>1181</v>
+        <v>1207</v>
       </c>
       <c r="H3" t="n">
         <v>37.72</v>
@@ -702,7 +702,7 @@
         <v>37.7</v>
       </c>
       <c r="O3" t="n">
-        <v>496909122700</v>
+        <v>504208646250</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>호실적 발표, 주식 소각 결정, 전망 상향 등 긍정적 공시 잇따름. 외인 매수세 및 숏커버링 기대.</t>
+          <t>삼성E&amp;A, 역대급 실적 발표와 자사주 소각 및 취득 결정. MSCI 편입 예상, 5천억 영업이익으로 주가 급등 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['어닝서프라이즈', '주식소각', '실적전망']</t>
+          <t>['어닝서프라이즈', '주식소각', 'MSCI']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,21 +751,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7430</v>
+        <v>7350</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+11.56%</t>
+          <t>'+10.36%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" t="n">
         <v>133</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>8277603860</v>
+        <v>8369019960</v>
       </c>
       <c r="P4" t="n">
         <v>8430</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1700</v>
+        <v>1734</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.59%</t>
+          <t>'+7.70%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F5" t="n">
         <v>44</v>
       </c>
       <c r="G5" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -886,7 +886,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>18359958254</v>
+        <v>18856991568</v>
       </c>
       <c r="P5" t="n">
         <v>3980</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>푸드나무, 보호예수 해제 및 인수설 속 주가 변동성 확대. 주가 조작 의혹 제기.</t>
+          <t>푸드나무, 인수설 및 보호예수 해제 물량에도 불구하고 주가 변동성. 하한가 두 번 기록 후 반등 시도.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['보호예수 해제', '인수설', '주가 조작']</t>
+          <t>['보호예수', '인수설', '주가조작']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -952,7 +952,7 @@
         <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H6" t="n">
         <v>3.29</v>
@@ -978,7 +978,7 @@
         <v>3.61</v>
       </c>
       <c r="O6" t="n">
-        <v>67212052875</v>
+        <v>67513268405</v>
       </c>
       <c r="P6" t="n">
         <v>22450</v>
@@ -1038,13 +1038,13 @@
         <v>0.13</v>
       </c>
       <c r="E7" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F7" t="n">
         <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="H7" t="n">
         <v>9.949999999999999</v>
@@ -1070,7 +1070,7 @@
         <v>9.82</v>
       </c>
       <c r="O7" t="n">
-        <v>31959005585</v>
+        <v>32348103895</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14070</v>
+        <v>14080</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.68%</t>
+          <t>'-1.61%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.33</v>
       </c>
       <c r="E8" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F8" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G8" t="n">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="H8" t="n">
         <v>3.48</v>
@@ -1162,7 +1162,7 @@
         <v>3.15</v>
       </c>
       <c r="O8" t="n">
-        <v>85787176605</v>
+        <v>86887098410</v>
       </c>
       <c r="P8" t="n">
         <v>31500</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>AI 광통신 관련 기술 확보 소식 및 EUV용 유리기판 제조 기술 주목. 기관 매집 시작 기대감.</t>
+          <t>대한광통신, EUV용 유리기판 제조 기술 확보 및 AI 광통신 열풍으로 인한 주가 상승 기대. 기관 매집 시작.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['AI광통신', '유리기판', '기관매집']</t>
+          <t>['EUV', 'AI광통신', '기관매집']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1222,13 +1222,13 @@
         <v>-0.14</v>
       </c>
       <c r="E9" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G9" t="n">
-        <v>697</v>
+        <v>708</v>
       </c>
       <c r="H9" t="n">
         <v>13.09</v>
@@ -1254,7 +1254,7 @@
         <v>13.23</v>
       </c>
       <c r="O9" t="n">
-        <v>9148827200</v>
+        <v>9359552475</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7200</v>
+        <v>7210</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.04%</t>
+          <t>'-1.90%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.02</v>
       </c>
       <c r="E10" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F10" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G10" t="n">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="H10" t="n">
         <v>25.47</v>
@@ -1346,7 +1346,7 @@
         <v>25.45</v>
       </c>
       <c r="O10" t="n">
-        <v>9084000655</v>
+        <v>9212884705</v>
       </c>
       <c r="P10" t="n">
         <v>17950</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>216000</v>
+        <v>216250</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.36%</t>
+          <t>'-3.24%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="G11" t="n">
-        <v>1358</v>
+        <v>1351</v>
       </c>
       <c r="H11" t="n">
         <v>46.14</v>
@@ -1438,7 +1438,7 @@
         <v>46.08</v>
       </c>
       <c r="O11" t="n">
-        <v>1212999818500</v>
+        <v>1228224015750</v>
       </c>
       <c r="P11" t="n">
         <v>374500</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 이슈와 함께 개인 투자자 매도세 지속. 증시 하락 전망 및 불안감 고조.</t>
+          <t>삼성전자, 정치적 이슈와 외국인 매도세로 인한 주가 하락. 향후 2-3% 추가 하락 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['증시하락', '주가조작', '외국인매도']</t>
+          <t>['주가부양', '외국인매도', '국가시스템']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1504,7 +1504,7 @@
         <v>44</v>
       </c>
       <c r="G12" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H12" t="n">
         <v>1.2</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>72085955400</v>
+        <v>72440961120</v>
       </c>
       <c r="P12" t="n">
         <v>28800</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9750</v>
+        <v>9780</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.32%</t>
+          <t>'-4.02%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.53</v>
       </c>
       <c r="E13" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F13" t="n">
         <v>63</v>
       </c>
       <c r="G13" t="n">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="H13" t="n">
         <v>5.87</v>
@@ -1622,7 +1622,7 @@
         <v>5.34</v>
       </c>
       <c r="O13" t="n">
-        <v>13533384050</v>
+        <v>13742579830</v>
       </c>
       <c r="P13" t="n">
         <v>14940</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>테슬라 실적 발표 및 스페이스X 관련 뉴스에도 불구하고 주가 하락 및 공매도 우려.</t>
+          <t>명신산업, 테슬라 실적 호조 및 스페이스X 관련 뉴스에도 불구하고 큰 손 물량 출회 및 공매도 압박으로 인한 주가 변동성.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1238000</v>
+        <v>1239000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.33%</t>
+          <t>'-4.25%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1688,7 +1688,7 @@
         <v>503</v>
       </c>
       <c r="G14" t="n">
-        <v>1687</v>
+        <v>1724</v>
       </c>
       <c r="H14" t="n">
         <v>48.79</v>
@@ -1708,13 +1708,13 @@
         <v>1297000</v>
       </c>
       <c r="M14" t="n">
-        <v>1238000</v>
+        <v>1233000</v>
       </c>
       <c r="N14" t="n">
         <v>48.77</v>
       </c>
       <c r="O14" t="n">
-        <v>1452608194000</v>
+        <v>1488522572000</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 이슈와 맞물려 반도체 산업 하락 및 주가 하락세 지속. 외국인 매도세 관찰.</t>
+          <t>SK하이닉스, 정치적 이슈와 반도체 산업 성장 둔화 우려로 인한 외국인 매도세 지속. 최태원 회장 발언은 긍정적이나 시장 분위기 하락.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['반도체산업', '주가하락', '외국인매도']</t>
+          <t>['반도체', '외국인매도', '우상향']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10070</v>
+        <v>10150</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-9.61%</t>
+          <t>'-8.89%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>2.41</v>
       </c>
       <c r="E15" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F15" t="n">
         <v>82</v>
       </c>
       <c r="G15" t="n">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="H15" t="n">
         <v>3.69</v>
@@ -1806,7 +1806,7 @@
         <v>1.28</v>
       </c>
       <c r="O15" t="n">
-        <v>52916716375</v>
+        <v>53394454745</v>
       </c>
       <c r="P15" t="n">
         <v>11690</v>

--- a/data/trending_integrated_20261022_12.xlsx
+++ b/data/trending_integrated_20261022_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3695</v>
+        <v>3665</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+19.58%</t>
+          <t>'+18.61%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="F2" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G2" t="n">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>62167598262</v>
+        <v>63075122050</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>빅텍, 김정은 신변 이상설 및 사망설로 인한 급등. 전쟁 가능성 대두 및 단기 차익 실현 움직임.</t>
+          <t>김정은 신변 이상설 및 사망설로 인한 급등락 반복. 전쟁 가능성 대두.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['김정은', '신변이상설', '전쟁가능성']</t>
+          <t>['신변 이상설', '사망설', '전쟁 가능성']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55300</v>
+        <v>55400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.93%</t>
+          <t>'+16.14%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F3" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G3" t="n">
-        <v>1207</v>
+        <v>1233</v>
       </c>
       <c r="H3" t="n">
         <v>37.72</v>
@@ -702,7 +702,7 @@
         <v>37.7</v>
       </c>
       <c r="O3" t="n">
-        <v>504208646250</v>
+        <v>508166501050</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>삼성E&amp;A, 역대급 실적 발표와 자사주 소각 및 취득 결정. MSCI 편입 예상, 5천억 영업이익으로 주가 급등 전망.</t>
+          <t>실적 발표 어닝 서프라이즈 및 주식 소각 결정, 영업이익 5000억 달성. MSCI 편입 예상.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['어닝서프라이즈', '주식소각', 'MSCI']</t>
+          <t>['어닝 서프라이즈', '주식 소각', '영업이익']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7350</v>
+        <v>7360</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+10.36%</t>
+          <t>'+10.51%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>8369019960</v>
+        <v>8445773340</v>
       </c>
       <c r="P4" t="n">
         <v>8430</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1734</v>
+        <v>1728</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.70%</t>
+          <t>'+7.33%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="F5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G5" t="n">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -886,7 +886,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>18856991568</v>
+        <v>19552876829</v>
       </c>
       <c r="P5" t="n">
         <v>3980</v>
@@ -902,12 +902,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>푸드나무, 인수설 및 보호예수 해제 물량에도 불구하고 주가 변동성. 하한가 두 번 기록 후 반등 시도.</t>
+          <t>보호예수 해제 물량 및 인수설 언급. 주가조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18200</v>
+        <v>18320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.56%</t>
+          <t>'+2.23%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.32</v>
       </c>
       <c r="E6" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F6" t="n">
         <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H6" t="n">
         <v>3.29</v>
@@ -978,7 +978,7 @@
         <v>3.61</v>
       </c>
       <c r="O6" t="n">
-        <v>67513268405</v>
+        <v>67688175265</v>
       </c>
       <c r="P6" t="n">
         <v>22450</v>
@@ -1038,13 +1038,13 @@
         <v>0.13</v>
       </c>
       <c r="E7" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G7" t="n">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="H7" t="n">
         <v>9.949999999999999</v>
@@ -1070,7 +1070,7 @@
         <v>9.82</v>
       </c>
       <c r="O7" t="n">
-        <v>32348103895</v>
+        <v>32732483580</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14080</v>
+        <v>41600</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.61%</t>
+          <t>'-1.77%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.33</v>
+        <v>-0.14</v>
       </c>
       <c r="E8" t="n">
-        <v>108</v>
+        <v>176</v>
       </c>
       <c r="F8" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="G8" t="n">
-        <v>409</v>
+        <v>732</v>
       </c>
       <c r="H8" t="n">
-        <v>3.48</v>
+        <v>13.09</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14310</v>
+        <v>42350</v>
       </c>
       <c r="K8" t="n">
-        <v>14180</v>
+        <v>41850</v>
       </c>
       <c r="L8" t="n">
-        <v>14830</v>
+        <v>42350</v>
       </c>
       <c r="M8" t="n">
-        <v>13890</v>
+        <v>41150</v>
       </c>
       <c r="N8" t="n">
-        <v>3.15</v>
+        <v>13.23</v>
       </c>
       <c r="O8" t="n">
-        <v>86887098410</v>
+        <v>9478030400</v>
       </c>
       <c r="P8" t="n">
-        <v>31500</v>
+        <v>69200</v>
       </c>
       <c r="Q8" t="n">
-        <v>1640</v>
+        <v>24150</v>
       </c>
       <c r="R8" t="n">
-        <v>-389000</v>
+        <v>18000</v>
       </c>
       <c r="S8" t="n">
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>대한광통신, EUV용 유리기판 제조 기술 확보 및 AI 광통신 열풍으로 인한 주가 상승 기대. 기관 매집 시작.</t>
+          <t>간암 치료제 CRL 수령 이후 클래스 1 또는 즉시 승인 기대감 표출. FDA 승인 요건 미충족 가능성에 대한 신중론과 긍정론 혼재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['EUV', 'AI광통신', '기관매집']</t>
+          <t>['간암 치료제', 'FDA 승인', 'CRL']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,18 +1200,18 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41600</v>
+        <v>7220</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1219,71 +1219,71 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.14</v>
+        <v>0.02</v>
       </c>
       <c r="E9" t="n">
-        <v>174</v>
+        <v>118</v>
       </c>
       <c r="F9" t="n">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="G9" t="n">
-        <v>708</v>
+        <v>435</v>
       </c>
       <c r="H9" t="n">
-        <v>13.09</v>
+        <v>25.47</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>42350</v>
+        <v>7350</v>
       </c>
       <c r="K9" t="n">
-        <v>41850</v>
+        <v>7270</v>
       </c>
       <c r="L9" t="n">
-        <v>42350</v>
+        <v>7340</v>
       </c>
       <c r="M9" t="n">
-        <v>41150</v>
+        <v>7170</v>
       </c>
       <c r="N9" t="n">
-        <v>13.23</v>
+        <v>25.45</v>
       </c>
       <c r="O9" t="n">
-        <v>9359552475</v>
+        <v>9374696185</v>
       </c>
       <c r="P9" t="n">
-        <v>69200</v>
+        <v>17950</v>
       </c>
       <c r="Q9" t="n">
-        <v>24150</v>
+        <v>7170</v>
       </c>
       <c r="R9" t="n">
-        <v>18000</v>
+        <v>-180000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-31000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>간암 치료제 CRL 수령 이후 클래스 1 또는 즉시 승인 기대감 표출. FDA 승인 요건 미충족 가능성에 대한 신중론과 긍정론 혼재.</t>
+          <t>연이은 적자 발표 및 주가 하락세 지속. 30년 최저가 수준 기록, PBR 0.57로 저평가 논란.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['간암 치료제', 'FDA 승인', 'CRL']</t>
+          <t>['영업손실', '신저가', 'PBR']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7210</v>
+        <v>14050</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.90%</t>
+          <t>'-1.82%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.02</v>
+        <v>0.33</v>
       </c>
       <c r="E10" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="F10" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="G10" t="n">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="H10" t="n">
-        <v>25.47</v>
+        <v>3.48</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>7350</v>
+        <v>14310</v>
       </c>
       <c r="K10" t="n">
-        <v>7270</v>
+        <v>14180</v>
       </c>
       <c r="L10" t="n">
-        <v>7340</v>
+        <v>14830</v>
       </c>
       <c r="M10" t="n">
-        <v>7170</v>
+        <v>13890</v>
       </c>
       <c r="N10" t="n">
-        <v>25.45</v>
+        <v>3.15</v>
       </c>
       <c r="O10" t="n">
-        <v>9212884705</v>
+        <v>87767594710</v>
       </c>
       <c r="P10" t="n">
-        <v>17950</v>
+        <v>31500</v>
       </c>
       <c r="Q10" t="n">
-        <v>7170</v>
+        <v>1640</v>
       </c>
       <c r="R10" t="n">
-        <v>-180000</v>
+        <v>-389000</v>
       </c>
       <c r="S10" t="n">
-        <v>-31000</v>
+        <v>16000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>연이은 적자 발표 및 주가 하락세 지속. 30년 최저가 수준 기록, PBR 0.57로 저평가 논란.</t>
+          <t>EUV용 유리기판 제조 기술 확보 및 AI 광통신 관련 뉴스. 기관 매집 시작.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['영업손실', '신저가', 'PBR']</t>
+          <t>['EUV', '유리기판', 'AI 광통신']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>216250</v>
+        <v>215750</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.24%</t>
+          <t>'-3.47%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>498</v>
+        <v>513</v>
       </c>
       <c r="G11" t="n">
-        <v>1351</v>
+        <v>1368</v>
       </c>
       <c r="H11" t="n">
         <v>46.14</v>
@@ -1438,7 +1438,7 @@
         <v>46.08</v>
       </c>
       <c r="O11" t="n">
-        <v>1228224015750</v>
+        <v>1301338607500</v>
       </c>
       <c r="P11" t="n">
         <v>374500</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>삼성전자, 정치적 이슈와 외국인 매도세로 인한 주가 하락. 향후 2-3% 추가 하락 전망.</t>
+          <t>정치적 이슈와 개인 투자자 매도세 지속. 국가 시스템 붕괴 우려.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주가부양', '외국인매도', '국가시스템']</t>
+          <t>['주가 부양', '국가 시스템', '매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,79 +1483,79 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14410</v>
+        <v>9820</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.81%</t>
+          <t>'-3.63%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.2</v>
+        <v>0.53</v>
       </c>
       <c r="E12" t="n">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="F12" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="G12" t="n">
-        <v>134</v>
+        <v>315</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2</v>
+        <v>5.87</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14980</v>
+        <v>10190</v>
       </c>
       <c r="K12" t="n">
-        <v>14460</v>
+        <v>10110</v>
       </c>
       <c r="L12" t="n">
-        <v>16140</v>
+        <v>10180</v>
       </c>
       <c r="M12" t="n">
-        <v>13550</v>
+        <v>9620</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="O12" t="n">
-        <v>72440961120</v>
+        <v>13975902350</v>
       </c>
       <c r="P12" t="n">
-        <v>28800</v>
+        <v>14940</v>
       </c>
       <c r="Q12" t="n">
-        <v>12030</v>
+        <v>5390</v>
       </c>
       <c r="R12" t="n">
-        <v>-54000</v>
+        <v>-32000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>AI, 반도체 관련 뉴스 및 신규 상장주 영향 속 주가 등락. 수주잔고 및 시총 관련 언급.</t>
+          <t>테슬라 실적 상회 및 스페이스X 관련 뉴스, 하지만 주가 연속성 부족.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['AI', '반도체', '수주잔고']</t>
+          <t>['테슬라', '스페이스X', '실적']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1563,91 +1563,91 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9780</v>
+        <v>14420</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.02%</t>
+          <t>'-3.74%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.53</v>
+        <v>1.2</v>
       </c>
       <c r="E13" t="n">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="F13" t="n">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="G13" t="n">
-        <v>309</v>
+        <v>136</v>
       </c>
       <c r="H13" t="n">
-        <v>5.87</v>
+        <v>1.2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>10190</v>
+        <v>14980</v>
       </c>
       <c r="K13" t="n">
-        <v>10110</v>
+        <v>14460</v>
       </c>
       <c r="L13" t="n">
-        <v>10180</v>
+        <v>16140</v>
       </c>
       <c r="M13" t="n">
-        <v>9620</v>
+        <v>13550</v>
       </c>
       <c r="N13" t="n">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>13742579830</v>
+        <v>72634557240</v>
       </c>
       <c r="P13" t="n">
-        <v>14940</v>
+        <v>28800</v>
       </c>
       <c r="Q13" t="n">
-        <v>5390</v>
+        <v>12030</v>
       </c>
       <c r="R13" t="n">
-        <v>-32000</v>
+        <v>-54000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>명신산업, 테슬라 실적 호조 및 스페이스X 관련 뉴스에도 불구하고 큰 손 물량 출회 및 공매도 압박으로 인한 주가 변동성.</t>
+          <t>AI, 반도체 관련 뉴스 및 신규 상장주 영향 속 주가 등락. 수주잔고 및 시총 관련 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['테슬라', '스페이스X', '공매도']</t>
+          <t>['AI', '반도체', '수주잔고']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1239000</v>
+        <v>1238000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.25%</t>
+          <t>'-4.33%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1688,7 +1688,7 @@
         <v>503</v>
       </c>
       <c r="G14" t="n">
-        <v>1724</v>
+        <v>1717</v>
       </c>
       <c r="H14" t="n">
         <v>48.79</v>
@@ -1714,7 +1714,7 @@
         <v>48.77</v>
       </c>
       <c r="O14" t="n">
-        <v>1488522572000</v>
+        <v>1556616942500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>SK하이닉스, 정치적 이슈와 반도체 산업 성장 둔화 우려로 인한 외국인 매도세 지속. 최태원 회장 발언은 긍정적이나 시장 분위기 하락.</t>
+          <t>정치적 이슈에 따른 한국 증시 및 반도체 산업 우려 제기.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['반도체', '외국인매도', '우상향']</t>
+          <t>['반도체', '증시', '정치']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10150</v>
+        <v>10120</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-8.89%</t>
+          <t>'-9.16%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>2.41</v>
       </c>
       <c r="E15" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F15" t="n">
         <v>82</v>
       </c>
       <c r="G15" t="n">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="H15" t="n">
         <v>3.69</v>
@@ -1806,7 +1806,7 @@
         <v>1.28</v>
       </c>
       <c r="O15" t="n">
-        <v>53394454745</v>
+        <v>54060362250</v>
       </c>
       <c r="P15" t="n">
         <v>11690</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>로봇주 급등 후 조정 구간 진입, 투기적 매매 경계. ESS 마진율 불확실성 및 주가 하락 우려.</t>
+          <t>로봇주 강세 속 투기 과열 예고 및 급락. ESS 마진율 불확실성.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['로봇주', '투기', 'ESS마진율']</t>
+          <t>['로봇주', '투기 과열', 'ESS']</t>
         </is>
       </c>
       <c r="X15" t="n">

--- a/data/trending_integrated_20261022_12.xlsx
+++ b/data/trending_integrated_20261022_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3665</v>
+        <v>3650</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+18.61%</t>
+          <t>'+18.12%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F2" t="n">
         <v>136</v>
       </c>
       <c r="G2" t="n">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>63075122050</v>
+        <v>63930722437</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>김정은 신변 이상설 및 사망설로 인한 급등락 반복. 전쟁 가능성 대두.</t>
+          <t>빅텍, 김정은 신변 이상설 및 전쟁 가능성 대두로 인한 급등세. 과거 급등 사례 언급하며 추가 상승 기대감 표출. 단타 매매 심리 작용.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신변 이상설', '사망설', '전쟁 가능성']</t>
+          <t>['김정은 신변이상설', '전쟁 가능성', '단기 급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55400</v>
+        <v>55200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.14%</t>
+          <t>'+15.72%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="F3" t="n">
         <v>167</v>
       </c>
       <c r="G3" t="n">
-        <v>1233</v>
+        <v>1255</v>
       </c>
       <c r="H3" t="n">
         <v>37.72</v>
@@ -702,7 +702,7 @@
         <v>37.7</v>
       </c>
       <c r="O3" t="n">
-        <v>508166501050</v>
+        <v>514645903800</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>실적 발표 어닝 서프라이즈 및 주식 소각 결정, 영업이익 5000억 달성. MSCI 편입 예상.</t>
+          <t>삼성E&amp;A, 실적 발표와 함께 어닝 서프라이즈 기록. 주식 소각 결정, 영업실적 수정 및 전망 상향 공시로 긍정적 흐름 예상. MSCI 편입 기대감도 존재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['어닝 서프라이즈', '주식 소각', '영업이익']</t>
+          <t>['어닝 서프라이즈', '주식 소각', '전망 상향']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>8445773340</v>
+        <v>8488235950</v>
       </c>
       <c r="P4" t="n">
         <v>8430</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1728</v>
+        <v>1702</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.33%</t>
+          <t>'+5.71%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F5" t="n">
         <v>46</v>
       </c>
       <c r="G5" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -886,7 +886,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>19552876829</v>
+        <v>19907204525</v>
       </c>
       <c r="P5" t="n">
         <v>3980</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>보호예수 해제 물량 및 인수설 언급. 주가조작 의혹 제기.</t>
+          <t>푸드나무, 보호예수 해제 물량 및 인수설 관련 내용 언급. 주가 조작 의혹과 함께 기대와 실망이 교차하는 반응.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['보호예수', '인수설', '주가조작']</t>
+          <t>['보호예수 해제', '인수설', '주가 조작']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18320</v>
+        <v>18160</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.23%</t>
+          <t>'+1.34%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H6" t="n">
         <v>3.29</v>
@@ -972,13 +972,13 @@
         <v>20150</v>
       </c>
       <c r="M6" t="n">
-        <v>18100</v>
+        <v>18090</v>
       </c>
       <c r="N6" t="n">
         <v>3.61</v>
       </c>
       <c r="O6" t="n">
-        <v>67688175265</v>
+        <v>68088051765</v>
       </c>
       <c r="P6" t="n">
         <v>22450</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14820</v>
+        <v>14760</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.34%</t>
+          <t>'-0.07%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.13</v>
       </c>
       <c r="E7" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F7" t="n">
         <v>40</v>
       </c>
       <c r="G7" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H7" t="n">
         <v>9.949999999999999</v>
@@ -1070,7 +1070,7 @@
         <v>9.82</v>
       </c>
       <c r="O7" t="n">
-        <v>32732483580</v>
+        <v>33175978020</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1115,83 +1115,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>41600</v>
+        <v>7210</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.77%</t>
+          <t>'-1.90%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.14</v>
+        <v>0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>176</v>
+        <v>120</v>
       </c>
       <c r="F8" t="n">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="G8" t="n">
-        <v>732</v>
+        <v>443</v>
       </c>
       <c r="H8" t="n">
-        <v>13.09</v>
+        <v>25.47</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>42350</v>
+        <v>7350</v>
       </c>
       <c r="K8" t="n">
-        <v>41850</v>
+        <v>7270</v>
       </c>
       <c r="L8" t="n">
-        <v>42350</v>
+        <v>7340</v>
       </c>
       <c r="M8" t="n">
-        <v>41150</v>
+        <v>7170</v>
       </c>
       <c r="N8" t="n">
-        <v>13.23</v>
+        <v>25.45</v>
       </c>
       <c r="O8" t="n">
-        <v>9478030400</v>
+        <v>9527599785</v>
       </c>
       <c r="P8" t="n">
-        <v>69200</v>
+        <v>17950</v>
       </c>
       <c r="Q8" t="n">
-        <v>24150</v>
+        <v>7170</v>
       </c>
       <c r="R8" t="n">
-        <v>18000</v>
+        <v>-180000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-31000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>간암 치료제 CRL 수령 이후 클래스 1 또는 즉시 승인 기대감 표출. FDA 승인 요건 미충족 가능성에 대한 신중론과 긍정론 혼재.</t>
+          <t>LG디스플레이, 지속적인 적자와 주가 하락세에 대한 절망적인 반응. 과거 투자 대비 성과 부진 및 신저가 기록으로 부정적 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['간암 치료제', 'FDA 승인', 'CRL']</t>
+          <t>['영업손실', '주가 폭락', '신저가']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7220</v>
+        <v>41350</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.77%</t>
+          <t>'-2.36%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.02</v>
+        <v>-0.14</v>
       </c>
       <c r="E9" t="n">
-        <v>118</v>
+        <v>178</v>
       </c>
       <c r="F9" t="n">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="G9" t="n">
-        <v>435</v>
+        <v>745</v>
       </c>
       <c r="H9" t="n">
-        <v>25.47</v>
+        <v>13.09</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>7350</v>
+        <v>42350</v>
       </c>
       <c r="K9" t="n">
-        <v>7270</v>
+        <v>41850</v>
       </c>
       <c r="L9" t="n">
-        <v>7340</v>
+        <v>42350</v>
       </c>
       <c r="M9" t="n">
-        <v>7170</v>
+        <v>41150</v>
       </c>
       <c r="N9" t="n">
-        <v>25.45</v>
+        <v>13.23</v>
       </c>
       <c r="O9" t="n">
-        <v>9374696185</v>
+        <v>9733416200</v>
       </c>
       <c r="P9" t="n">
-        <v>17950</v>
+        <v>69200</v>
       </c>
       <c r="Q9" t="n">
-        <v>7170</v>
+        <v>24150</v>
       </c>
       <c r="R9" t="n">
-        <v>-180000</v>
+        <v>18000</v>
       </c>
       <c r="S9" t="n">
-        <v>-31000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>연이은 적자 발표 및 주가 하락세 지속. 30년 최저가 수준 기록, PBR 0.57로 저평가 논란.</t>
+          <t>FDA 승인에 대한 기대와 우려 혼재. 기관 수급은 긍정적이나, 승인 불확실성 및 부정적 전망도 존재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['영업손실', '신저가', 'PBR']</t>
+          <t>['FDA 승인', '기관 수급', '간암 치료제']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14050</v>
+        <v>13950</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.82%</t>
+          <t>'-2.52%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.33</v>
       </c>
       <c r="E10" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F10" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G10" t="n">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="H10" t="n">
         <v>3.48</v>
@@ -1346,7 +1346,7 @@
         <v>3.15</v>
       </c>
       <c r="O10" t="n">
-        <v>87767594710</v>
+        <v>89558656200</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>EUV용 유리기판 제조 기술 확보 및 AI 광통신 관련 뉴스. 기관 매집 시작.</t>
+          <t>대한광통신, EUV용 유리기판 제조 기술 확보 및 AI 광통신 관련 뉴스 부각. 엔비디아, 삼성전자 등과의 연관성 언급하며 긍정적 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['EUV', '유리기판', 'AI 광통신']</t>
+          <t>['EUV 유리기판', 'AI 광통신', '기술 확보']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>215750</v>
+        <v>214750</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.47%</t>
+          <t>'-3.91%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="G11" t="n">
-        <v>1368</v>
+        <v>1399</v>
       </c>
       <c r="H11" t="n">
         <v>46.14</v>
@@ -1432,13 +1432,13 @@
         <v>226000</v>
       </c>
       <c r="M11" t="n">
-        <v>215000</v>
+        <v>214500</v>
       </c>
       <c r="N11" t="n">
         <v>46.08</v>
       </c>
       <c r="O11" t="n">
-        <v>1301338607500</v>
+        <v>1357957118750</v>
       </c>
       <c r="P11" t="n">
         <v>374500</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 이슈와 개인 투자자 매도세 지속. 국가 시스템 붕괴 우려.</t>
+          <t>삼성전자, 정치적 이슈와 거시 경제 악재로 인한 하락세. 일부에서는 주가 조작 및 투자금 손실 우려 제기. 향후 시장 전망에 대한 부정적 의견 다수.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주가 부양', '국가 시스템', '매도']</t>
+          <t>['국가 시스템', '증시 하락', '노무라 전망']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9820</v>
+        <v>9780</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.63%</t>
+          <t>'-4.02%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.53</v>
       </c>
       <c r="E12" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F12" t="n">
         <v>63</v>
       </c>
       <c r="G12" t="n">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="H12" t="n">
         <v>5.87</v>
@@ -1530,7 +1530,7 @@
         <v>5.34</v>
       </c>
       <c r="O12" t="n">
-        <v>13975902350</v>
+        <v>14159839450</v>
       </c>
       <c r="P12" t="n">
         <v>14940</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>테슬라 실적 상회 및 스페이스X 관련 뉴스, 하지만 주가 연속성 부족.</t>
+          <t>명신산업, 테슬라 실적 상회 및 스페이스X 관련 뉴스로 인한 기대감 형성. 다만, 주가 변동성과 공매도에 대한 우려도 공존.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['테슬라', '스페이스X', '실적']</t>
+          <t>['테슬라 실적', '스페이스X', '공매도']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,175 +1575,175 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14420</v>
+        <v>1232000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.74%</t>
+          <t>'-4.79%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.2</v>
+        <v>0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>78</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>44</v>
+        <v>514</v>
       </c>
       <c r="G13" t="n">
-        <v>136</v>
+        <v>1717</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2</v>
+        <v>48.79</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>14980</v>
+        <v>1294000</v>
       </c>
       <c r="K13" t="n">
-        <v>14460</v>
+        <v>1273000</v>
       </c>
       <c r="L13" t="n">
-        <v>16140</v>
+        <v>1297000</v>
       </c>
       <c r="M13" t="n">
-        <v>13550</v>
+        <v>1229000</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>48.77</v>
       </c>
       <c r="O13" t="n">
-        <v>72634557240</v>
+        <v>1611672695500</v>
       </c>
       <c r="P13" t="n">
-        <v>28800</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>12030</v>
+        <v>468000</v>
       </c>
       <c r="R13" t="n">
-        <v>-54000</v>
+        <v>-55000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-6000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>AI, 반도체 관련 뉴스 및 신규 상장주 영향 속 주가 등락. 수주잔고 및 시총 관련 언급.</t>
+          <t>SK하이닉스, 정치적 이슈와 맞물린 증시 전반의 하락세 영향. 반도체 산업 전망에 대한 회의론과 함께 주가 부양에 대한 요구 존재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['AI', '반도체', '수주잔고']</t>
+          <t>['증시 조작', '반도체 사이클', '주가 우상향']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1238000</v>
+        <v>14230</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.33%</t>
+          <t>'-5.01%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.02</v>
+        <v>1.2</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>80</v>
       </c>
       <c r="F14" t="n">
-        <v>503</v>
+        <v>44</v>
       </c>
       <c r="G14" t="n">
-        <v>1717</v>
+        <v>136</v>
       </c>
       <c r="H14" t="n">
-        <v>48.79</v>
+        <v>1.2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1294000</v>
+        <v>14980</v>
       </c>
       <c r="K14" t="n">
-        <v>1273000</v>
+        <v>14460</v>
       </c>
       <c r="L14" t="n">
-        <v>1297000</v>
+        <v>16140</v>
       </c>
       <c r="M14" t="n">
-        <v>1233000</v>
+        <v>13550</v>
       </c>
       <c r="N14" t="n">
-        <v>48.77</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1556616942500</v>
+        <v>73062626985</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>28800</v>
       </c>
       <c r="Q14" t="n">
-        <v>468000</v>
+        <v>12030</v>
       </c>
       <c r="R14" t="n">
-        <v>-55000</v>
+        <v>-54000</v>
       </c>
       <c r="S14" t="n">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 이슈에 따른 한국 증시 및 반도체 산업 우려 제기.</t>
+          <t>멜콘, 대만 반도체 파업 및 ASML 협조 관련 소식으로 인한 변동성. AI 및 반도체 관련 기대감 속에서 추가 성장 가능성 질의.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['반도체', '증시', '정치']</t>
+          <t>['ASML 협조', 'AI 반도체', '수율']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10120</v>
+        <v>10080</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-9.16%</t>
+          <t>'-9.52%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>2.41</v>
       </c>
       <c r="E15" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="F15" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G15" t="n">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="H15" t="n">
         <v>3.69</v>
@@ -1806,7 +1806,7 @@
         <v>1.28</v>
       </c>
       <c r="O15" t="n">
-        <v>54060362250</v>
+        <v>54738627700</v>
       </c>
       <c r="P15" t="n">
         <v>11690</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>로봇주 강세 속 투기 과열 예고 및 급락. ESS 마진율 불확실성.</t>
+          <t>HT로보틱스, 로봇주 및 NXT 시장 관련 기대감 있었으나 급락. 예상치 못한 조정과 ESS 마진율 불확실성 등으로 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['로봇주', '투기 과열', 'ESS']</t>
+          <t>['로봇주', 'NXT 시장', 'ESS 마진율']</t>
         </is>
       </c>
       <c r="X15" t="n">

--- a/data/trending_integrated_20261022_12.xlsx
+++ b/data/trending_integrated_20261022_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3650</v>
+        <v>3605</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+18.12%</t>
+          <t>'+16.67%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="F2" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G2" t="n">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>63930722437</v>
+        <v>64707527019</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55200</v>
+        <v>55500</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.72%</t>
+          <t>'+16.35%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="F3" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G3" t="n">
-        <v>1255</v>
+        <v>1281</v>
       </c>
       <c r="H3" t="n">
         <v>37.72</v>
@@ -702,7 +702,7 @@
         <v>37.7</v>
       </c>
       <c r="O3" t="n">
-        <v>514645903800</v>
+        <v>521178571250</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7360</v>
+        <v>7340</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+10.51%</t>
+          <t>'+10.21%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G4" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>8488235950</v>
+        <v>8602733310</v>
       </c>
       <c r="P4" t="n">
         <v>8430</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1702</v>
+        <v>1704</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.71%</t>
+          <t>'+5.84%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G5" t="n">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -886,7 +886,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>19907204525</v>
+        <v>20196419358</v>
       </c>
       <c r="P5" t="n">
         <v>3980</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>푸드나무, 보호예수 해제 물량 및 인수설 관련 내용 언급. 주가 조작 의혹과 함께 기대와 실망이 교차하는 반응.</t>
+          <t>보호예수 해제 물량, 인수설 등 다양한 이슈 속에서 주가 변동성 예상. 일부 투자자들은 호재로 해석하며 매수를 권유.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['보호예수 해제', '인수설', '주가 조작']</t>
+          <t>['보호예수', '인수설', '주가 변동']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,18 +935,18 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18160</v>
+        <v>18010</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.34%</t>
+          <t>'+0.50%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.32</v>
       </c>
       <c r="E6" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F6" t="n">
         <v>42</v>
@@ -972,13 +972,13 @@
         <v>20150</v>
       </c>
       <c r="M6" t="n">
-        <v>18090</v>
+        <v>17980</v>
       </c>
       <c r="N6" t="n">
         <v>3.61</v>
       </c>
       <c r="O6" t="n">
-        <v>68088051765</v>
+        <v>68815211775</v>
       </c>
       <c r="P6" t="n">
         <v>22450</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14760</v>
+        <v>14750</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.07%</t>
+          <t>'-0.14%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.13</v>
       </c>
       <c r="E7" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F7" t="n">
         <v>40</v>
       </c>
       <c r="G7" t="n">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="H7" t="n">
         <v>9.949999999999999</v>
@@ -1070,7 +1070,7 @@
         <v>9.82</v>
       </c>
       <c r="O7" t="n">
-        <v>33175978020</v>
+        <v>33559052410</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>건설주 전반의 상승 기대감 속에서 외국인 및 연기금 매수세 관찰. 삼성E&amp;A 대비 낮은 상승률 지적.</t>
+          <t>삼성e&amp;a 대비 낮은 상승률에 대한 불만 제기. 외국인 및 연기금 매수세 언급에도 불구하고 주가 부진 지속. 주주들의 대차 해지 운동 촉구.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['건설주', '외국인매수', '실적우량주']</t>
+          <t>['건설주', '주가 부진', '대차 해지']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1130,13 +1130,13 @@
         <v>0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F8" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G8" t="n">
-        <v>443</v>
+        <v>472</v>
       </c>
       <c r="H8" t="n">
         <v>25.47</v>
@@ -1162,7 +1162,7 @@
         <v>25.45</v>
       </c>
       <c r="O8" t="n">
-        <v>9527599785</v>
+        <v>9735121575</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>LG디스플레이, 지속적인 적자와 주가 하락세에 대한 절망적인 반응. 과거 투자 대비 성과 부진 및 신저가 기록으로 부정적 전망.</t>
+          <t>연속적인 영업 손실 발표 및 30년 최저가 경신으로 인한 투자 심리 악화. 주주들은 회사의 방어를 위해 노력하지만, 주가는 하락세 지속.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['영업손실', '주가 폭락', '신저가']</t>
+          <t>['영업 손실', '주가 하락', '신저가']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41350</v>
+        <v>14020</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.36%</t>
+          <t>'-2.03%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.14</v>
+        <v>0.33</v>
       </c>
       <c r="E9" t="n">
-        <v>178</v>
+        <v>114</v>
       </c>
       <c r="F9" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="G9" t="n">
-        <v>745</v>
+        <v>441</v>
       </c>
       <c r="H9" t="n">
-        <v>13.09</v>
+        <v>3.48</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>42350</v>
+        <v>14310</v>
       </c>
       <c r="K9" t="n">
-        <v>41850</v>
+        <v>14180</v>
       </c>
       <c r="L9" t="n">
-        <v>42350</v>
+        <v>14830</v>
       </c>
       <c r="M9" t="n">
-        <v>41150</v>
+        <v>13890</v>
       </c>
       <c r="N9" t="n">
-        <v>13.23</v>
+        <v>3.15</v>
       </c>
       <c r="O9" t="n">
-        <v>9733416200</v>
+        <v>90234516140</v>
       </c>
       <c r="P9" t="n">
-        <v>69200</v>
+        <v>31500</v>
       </c>
       <c r="Q9" t="n">
-        <v>24150</v>
+        <v>1640</v>
       </c>
       <c r="R9" t="n">
-        <v>18000</v>
+        <v>-389000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>FDA 승인에 대한 기대와 우려 혼재. 기관 수급은 긍정적이나, 승인 불확실성 및 부정적 전망도 존재.</t>
+          <t>대한광통신, EUV용 유리기판 제조 기술 확보 및 AI 광통신 관련 뉴스 부각. 엔비디아, 삼성전자 등과의 연관성 언급하며 긍정적 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['FDA 승인', '기관 수급', '간암 치료제']</t>
+          <t>['EUV 유리기판', 'AI 광통신', '기술 확보']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13950</v>
+        <v>41450</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.52%</t>
+          <t>'-2.13%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.33</v>
+        <v>-0.14</v>
       </c>
       <c r="E10" t="n">
-        <v>113</v>
+        <v>182</v>
       </c>
       <c r="F10" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="G10" t="n">
-        <v>432</v>
+        <v>758</v>
       </c>
       <c r="H10" t="n">
-        <v>3.48</v>
+        <v>13.09</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>14310</v>
+        <v>42350</v>
       </c>
       <c r="K10" t="n">
-        <v>14180</v>
+        <v>41850</v>
       </c>
       <c r="L10" t="n">
-        <v>14830</v>
+        <v>42350</v>
       </c>
       <c r="M10" t="n">
-        <v>13890</v>
+        <v>41150</v>
       </c>
       <c r="N10" t="n">
-        <v>3.15</v>
+        <v>13.23</v>
       </c>
       <c r="O10" t="n">
-        <v>89558656200</v>
+        <v>10128986550</v>
       </c>
       <c r="P10" t="n">
-        <v>31500</v>
+        <v>69200</v>
       </c>
       <c r="Q10" t="n">
-        <v>1640</v>
+        <v>24150</v>
       </c>
       <c r="R10" t="n">
-        <v>-389000</v>
+        <v>18000</v>
       </c>
       <c r="S10" t="n">
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>대한광통신, EUV용 유리기판 제조 기술 확보 및 AI 광통신 관련 뉴스 부각. 엔비디아, 삼성전자 등과의 연관성 언급하며 긍정적 전망.</t>
+          <t>간암 치료제 FDA 승인 기대감. 기관 수급 유입 언급 및 진양곤 회장의 발언을 근거로 긍정적 전망 제시. C2 확률 및 승인 요건 분석.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['EUV 유리기판', 'AI 광통신', '기술 확보']</t>
+          <t>['FDA 승인', '간암 치료제', '기관 수급']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>214750</v>
+        <v>14660</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.91%</t>
+          <t>'-2.14%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.06</v>
+        <v>1.2</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>85</v>
       </c>
       <c r="F11" t="n">
-        <v>524</v>
+        <v>46</v>
       </c>
       <c r="G11" t="n">
-        <v>1399</v>
+        <v>152</v>
       </c>
       <c r="H11" t="n">
-        <v>46.14</v>
+        <v>1.2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>223500</v>
+        <v>14980</v>
       </c>
       <c r="K11" t="n">
-        <v>221500</v>
+        <v>14460</v>
       </c>
       <c r="L11" t="n">
-        <v>226000</v>
+        <v>16140</v>
       </c>
       <c r="M11" t="n">
-        <v>214500</v>
+        <v>13550</v>
       </c>
       <c r="N11" t="n">
-        <v>46.08</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1357957118750</v>
+        <v>74189513715</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>28800</v>
       </c>
       <c r="Q11" t="n">
-        <v>94500</v>
+        <v>12030</v>
       </c>
       <c r="R11" t="n">
-        <v>-677000</v>
+        <v>-54000</v>
       </c>
       <c r="S11" t="n">
-        <v>-254000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>삼성전자, 정치적 이슈와 거시 경제 악재로 인한 하락세. 일부에서는 주가 조작 및 투자금 손실 우려 제기. 향후 시장 전망에 대한 부정적 의견 다수.</t>
+          <t>조선일보, 대만 반도체 파업 등 다양한 뉴스 언급. 보호예수 해제일을 앞두고 주가 흔들림 예상되나, 일부 투자자들은 매수 기회로 판단.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['국가 시스템', '증시 하락', '노무라 전망']</t>
+          <t>['반도체', '보호예수', '뉴스']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9780</v>
+        <v>215250</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.02%</t>
+          <t>'-3.69%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.53</v>
+        <v>0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>115</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>63</v>
+        <v>536</v>
       </c>
       <c r="G12" t="n">
-        <v>324</v>
+        <v>1467</v>
       </c>
       <c r="H12" t="n">
-        <v>5.87</v>
+        <v>46.14</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>10190</v>
+        <v>223500</v>
       </c>
       <c r="K12" t="n">
-        <v>10110</v>
+        <v>221500</v>
       </c>
       <c r="L12" t="n">
-        <v>10180</v>
+        <v>226000</v>
       </c>
       <c r="M12" t="n">
-        <v>9620</v>
+        <v>214500</v>
       </c>
       <c r="N12" t="n">
-        <v>5.34</v>
+        <v>46.08</v>
       </c>
       <c r="O12" t="n">
-        <v>14159839450</v>
+        <v>1412549077500</v>
       </c>
       <c r="P12" t="n">
-        <v>14940</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>5390</v>
+        <v>94500</v>
       </c>
       <c r="R12" t="n">
-        <v>-32000</v>
+        <v>-677000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-254000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>명신산업, 테슬라 실적 상회 및 스페이스X 관련 뉴스로 인한 기대감 형성. 다만, 주가 변동성과 공매도에 대한 우려도 공존.</t>
+          <t>국가 시스템 붕괴 및 이재명 관련 악재로 인한 주가 하락 전망. 개인 투자자들의 매도세가 강하며, 노무라 증권은 한국 증시 하향 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['테슬라 실적', '스페이스X', '공매도']</t>
+          <t>['주가 하락', '악재', '전망']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1232000</v>
+        <v>9750</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.79%</t>
+          <t>'-4.32%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.02</v>
+        <v>0.53</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>115</v>
       </c>
       <c r="F13" t="n">
-        <v>514</v>
+        <v>62</v>
       </c>
       <c r="G13" t="n">
-        <v>1717</v>
+        <v>335</v>
       </c>
       <c r="H13" t="n">
-        <v>48.79</v>
+        <v>5.87</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1294000</v>
+        <v>10190</v>
       </c>
       <c r="K13" t="n">
-        <v>1273000</v>
+        <v>10110</v>
       </c>
       <c r="L13" t="n">
-        <v>1297000</v>
+        <v>10180</v>
       </c>
       <c r="M13" t="n">
-        <v>1229000</v>
+        <v>9620</v>
       </c>
       <c r="N13" t="n">
-        <v>48.77</v>
+        <v>5.34</v>
       </c>
       <c r="O13" t="n">
-        <v>1611672695500</v>
+        <v>14256081370</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>14940</v>
       </c>
       <c r="Q13" t="n">
-        <v>468000</v>
+        <v>5390</v>
       </c>
       <c r="R13" t="n">
-        <v>-55000</v>
+        <v>-32000</v>
       </c>
       <c r="S13" t="n">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>SK하이닉스, 정치적 이슈와 맞물린 증시 전반의 하락세 영향. 반도체 산업 전망에 대한 회의론과 함께 주가 부양에 대한 요구 존재.</t>
+          <t>테슬라 실적 호조 및 스페이스X 관련 뉴스로 기대감 형성. 다만, 개인 투자자들의 매도와 공매도 세력의 압박으로 주가 변동성이 큰 상황.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['증시 조작', '반도체 사이클', '주가 우상향']</t>
+          <t>['테슬라', '스페이스X', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14230</v>
+        <v>1236000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-5.01%</t>
+          <t>'-4.48%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.2</v>
+        <v>0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>44</v>
+        <v>523</v>
       </c>
       <c r="G14" t="n">
-        <v>136</v>
+        <v>1609</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2</v>
+        <v>48.79</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>14980</v>
+        <v>1294000</v>
       </c>
       <c r="K14" t="n">
-        <v>14460</v>
+        <v>1273000</v>
       </c>
       <c r="L14" t="n">
-        <v>16140</v>
+        <v>1297000</v>
       </c>
       <c r="M14" t="n">
-        <v>13550</v>
+        <v>1229000</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>48.77</v>
       </c>
       <c r="O14" t="n">
-        <v>73062626985</v>
+        <v>1664200089500</v>
       </c>
       <c r="P14" t="n">
-        <v>28800</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>12030</v>
+        <v>468000</v>
       </c>
       <c r="R14" t="n">
-        <v>-54000</v>
+        <v>-55000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-6000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>멜콘, 대만 반도체 파업 및 ASML 협조 관련 소식으로 인한 변동성. AI 및 반도체 관련 기대감 속에서 추가 성장 가능성 질의.</t>
+          <t>이재명 정부 및 최태원 회장의 경영 방식에 대한 비판. 솔리다임 상장 이슈와 공매도 금지 요구 언급. 반도체 업황 부진 우려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['ASML 협조', 'AI 반도체', '수율']</t>
+          <t>['이재명', '솔리다임', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10080</v>
+        <v>10100</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-9.52%</t>
+          <t>'-9.34%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>2.41</v>
       </c>
       <c r="E15" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F15" t="n">
         <v>84</v>
       </c>
       <c r="G15" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="H15" t="n">
         <v>3.69</v>
@@ -1806,7 +1806,7 @@
         <v>1.28</v>
       </c>
       <c r="O15" t="n">
-        <v>54738627700</v>
+        <v>55246199680</v>
       </c>
       <c r="P15" t="n">
         <v>11690</v>
